--- a/data/trans_dic/P1402-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1402-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,53</t>
+          <t>2,05; 6,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,96</t>
+          <t>4,41; 11,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,75</t>
+          <t>4,42; 11,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 14,88</t>
+          <t>8,07; 14,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,22</t>
+          <t>2,01; 7,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 9,74</t>
+          <t>3,95; 10,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,59</t>
+          <t>3,1; 8,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,13</t>
+          <t>5,9; 10,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,93</t>
+          <t>2,47; 5,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,09</t>
+          <t>4,99; 9,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,46</t>
+          <t>4,59; 8,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 11,4</t>
+          <t>7,61; 11,42</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,51</t>
+          <t>3,28; 7,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 9,91</t>
+          <t>4,85; 9,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,55</t>
+          <t>5,55; 10,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 10,84</t>
+          <t>5,65; 10,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,35</t>
+          <t>6,27; 11,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 14,08</t>
+          <t>8,39; 13,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 13,8</t>
+          <t>8,05; 13,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,67</t>
+          <t>6,51; 9,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,71</t>
+          <t>5,37; 8,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 11,0</t>
+          <t>7,31; 11,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,33</t>
+          <t>7,48; 11,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 10,0</t>
+          <t>6,67; 9,69</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,87</t>
+          <t>3,32; 8,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 13,71</t>
+          <t>6,97; 13,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,15</t>
+          <t>2,82; 6,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 13,9</t>
+          <t>8,01; 13,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,72</t>
+          <t>4,4; 10,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 14,35</t>
+          <t>7,3; 14,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 10,63</t>
+          <t>4,79; 10,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 11,97</t>
+          <t>7,18; 11,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,43</t>
+          <t>4,74; 8,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 12,83</t>
+          <t>7,72; 12,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,97</t>
+          <t>4,36; 8,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 12,02</t>
+          <t>8,2; 11,71</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,05</t>
+          <t>2,77; 7,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,91</t>
+          <t>4,05; 9,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 15,81</t>
+          <t>8,96; 15,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 12,07</t>
+          <t>6,37; 12,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 8,18</t>
+          <t>3,64; 7,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,83</t>
+          <t>5,96; 11,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,83</t>
+          <t>4,58; 9,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,64</t>
+          <t>5,32; 8,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,6</t>
+          <t>3,55; 6,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,36</t>
+          <t>5,57; 9,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,64</t>
+          <t>7,48; 11,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,89</t>
+          <t>6,35; 9,69</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 9,19</t>
+          <t>3,27; 9,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 14,11</t>
+          <t>5,67; 13,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 9,88</t>
+          <t>3,43; 9,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,27; 12,67</t>
+          <t>5,57; 11,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 14,52</t>
+          <t>5,93; 14,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 17,9</t>
+          <t>8,53; 17,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 13,07</t>
+          <t>5,49; 13,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,19; 16,02</t>
+          <t>9,95; 15,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,86</t>
+          <t>5,46; 10,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 14,93</t>
+          <t>8,21; 14,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 10,54</t>
+          <t>5,06; 10,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,1; 13,44</t>
+          <t>8,47; 12,75</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,18</t>
+          <t>2,89; 8,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 11,1</t>
+          <t>4,76; 11,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,47; 10,71</t>
+          <t>4,52; 10,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,89; 17,38</t>
+          <t>11,09; 17,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,04</t>
+          <t>2,17; 7,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,05; 14,43</t>
+          <t>7,12; 14,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,4; 11,02</t>
+          <t>4,21; 11,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,92</t>
+          <t>7,94; 12,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,93</t>
+          <t>2,87; 6,67</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,65; 11,51</t>
+          <t>6,67; 11,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,58</t>
+          <t>5,01; 9,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,31; 14,18</t>
+          <t>10,2; 14,53</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,87</t>
+          <t>4,87; 8,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,8</t>
+          <t>6,1; 10,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,94; 13,9</t>
+          <t>8,78; 13,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 11,67</t>
+          <t>7,49; 12,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,84</t>
+          <t>5,74; 9,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,74</t>
+          <t>6,56; 10,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,46; 11,37</t>
+          <t>6,43; 11,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,74</t>
+          <t>5,34; 8,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,66</t>
+          <t>5,67; 8,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,01; 9,94</t>
+          <t>6,86; 9,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,41; 12,01</t>
+          <t>8,39; 11,92</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,15</t>
+          <t>6,82; 9,46</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,75</t>
+          <t>5,06; 8,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,53</t>
+          <t>4,61; 8,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,89</t>
+          <t>7,73; 11,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,54</t>
+          <t>6,23; 9,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,65</t>
+          <t>5,05; 8,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,84</t>
+          <t>4,38; 7,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,44</t>
+          <t>7,07; 11,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,98</t>
+          <t>5,13; 7,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,03</t>
+          <t>5,42; 7,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,54</t>
+          <t>4,98; 7,59</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,82; 10,67</t>
+          <t>7,78; 10,79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,57</t>
+          <t>5,91; 8,17</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,43</t>
+          <t>4,98; 6,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,43</t>
+          <t>6,61; 8,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,91; 9,8</t>
+          <t>7,86; 9,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,84</t>
+          <t>8,37; 10,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,95; 7,66</t>
+          <t>5,96; 7,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,71; 9,62</t>
+          <t>7,71; 9,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,53</t>
+          <t>7,4; 9,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,75; 8,04</t>
+          <t>7,12; 8,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,71; 6,85</t>
+          <t>5,68; 6,88</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,76</t>
+          <t>7,47; 8,73</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,91; 9,31</t>
+          <t>7,91; 9,22</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,68</t>
+          <t>7,93; 9,05</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33423</t>
+          <t>35242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>59977</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5655; 17816</t>
+          <t>5585; 18182</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12825; 32304</t>
+          <t>12986; 32523</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13593; 31578</t>
+          <t>12976; 33605</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24512; 46329</t>
+          <t>25726; 46626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5780; 18826</t>
+          <t>5245; 18731</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11140; 27967</t>
+          <t>11359; 29714</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9005; 24799</t>
+          <t>8939; 24098</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16876; 29335</t>
+          <t>18657; 32058</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13788; 31670</t>
+          <t>13199; 31888</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27589; 52918</t>
+          <t>29044; 54832</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26009; 49261</t>
+          <t>26754; 49810</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45413; 68531</t>
+          <t>48306; 72479</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41463</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>43467</t>
+          <t>45172</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84930</t>
+          <t>87433</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17740; 37023</t>
+          <t>16168; 37398</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25454; 50111</t>
+          <t>24543; 49545</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28218; 53027</t>
+          <t>27903; 51069</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28920; 56060</t>
+          <t>29919; 55900</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32830; 57207</t>
+          <t>31575; 57928</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44168; 73762</t>
+          <t>43944; 72405</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43263; 72193</t>
+          <t>42105; 71964</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34246; 54888</t>
+          <t>35538; 54477</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53514; 86871</t>
+          <t>53520; 85980</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74468; 113193</t>
+          <t>75267; 114547</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76323; 116225</t>
+          <t>76691; 114240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70515; 103155</t>
+          <t>71745; 104196</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34067</t>
+          <t>33716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>32956</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66657</t>
+          <t>66673</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11210; 28269</t>
+          <t>10595; 27027</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22409; 44422</t>
+          <t>22576; 45133</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8461; 22764</t>
+          <t>8984; 21699</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25776; 43852</t>
+          <t>25270; 42930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14814; 32616</t>
+          <t>14769; 33690</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25238; 48920</t>
+          <t>24893; 49032</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16142; 35742</t>
+          <t>16106; 36713</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24927; 41782</t>
+          <t>25583; 42038</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30214; 55173</t>
+          <t>30979; 54402</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53932; 85360</t>
+          <t>51374; 84855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27174; 52224</t>
+          <t>28538; 52674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54320; 79910</t>
+          <t>55112; 78679</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27696</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26796</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54492</t>
+          <t>62029</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10117; 25282</t>
+          <t>9922; 25194</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15220; 33340</t>
+          <t>15158; 34100</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33780; 58495</t>
+          <t>33151; 57901</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20366; 37714</t>
+          <t>23786; 45905</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13325; 30385</t>
+          <t>13504; 29477</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24154; 46011</t>
+          <t>23175; 44848</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17370; 38081</t>
+          <t>17743; 38422</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16071; 36361</t>
+          <t>22450; 37788</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27165; 48203</t>
+          <t>25937; 49757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43978; 71387</t>
+          <t>42461; 72888</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55535; 88158</t>
+          <t>56624; 88275</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39912; 70102</t>
+          <t>50522; 77027</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>16746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27194</t>
+          <t>28598</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43086</t>
+          <t>45343</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6696; 18693</t>
+          <t>6646; 18894</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12097; 30002</t>
+          <t>12066; 29397</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7202; 20868</t>
+          <t>7250; 20838</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11216; 22645</t>
+          <t>11457; 23108</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12222; 30153</t>
+          <t>12311; 30818</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19258; 39308</t>
+          <t>18723; 38510</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12174; 28569</t>
+          <t>12006; 28776</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21183; 33294</t>
+          <t>22531; 35548</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21204; 44617</t>
+          <t>22458; 43072</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35489; 64520</t>
+          <t>35505; 61924</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23722; 45319</t>
+          <t>21764; 43868</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35192; 51964</t>
+          <t>36610; 55100</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37617</t>
+          <t>37888</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63474</t>
+          <t>64868</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7780; 22147</t>
+          <t>7813; 22552</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13323; 30425</t>
+          <t>13050; 30571</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11765; 28186</t>
+          <t>11895; 26991</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29374; 46870</t>
+          <t>30031; 47007</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6098; 19574</t>
+          <t>6029; 19632</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19603; 40128</t>
+          <t>19805; 39561</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12024; 30088</t>
+          <t>11489; 30092</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20217; 33133</t>
+          <t>20885; 33460</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17678; 38045</t>
+          <t>15753; 36636</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36733; 63558</t>
+          <t>36805; 64121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27069; 51346</t>
+          <t>26852; 49820</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>54254; 74608</t>
+          <t>54441; 77567</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55988</t>
+          <t>68157</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>40124</t>
+          <t>51229</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96112</t>
+          <t>119386</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29266; 54573</t>
+          <t>29949; 55046</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>41240; 71555</t>
+          <t>40460; 69148</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58676; 91262</t>
+          <t>57621; 91796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43090; 72111</t>
+          <t>53440; 85616</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>35993; 62822</t>
+          <t>36664; 63598</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>45714; 74497</t>
+          <t>45507; 73569</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44660; 78586</t>
+          <t>44477; 78943</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18456; 57120</t>
+          <t>41118; 62742</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>71785; 108581</t>
+          <t>71008; 105194</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95152; 134884</t>
+          <t>93114; 133333</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>113333; 161908</t>
+          <t>113109; 160711</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>53745; 119536</t>
+          <t>101198; 140422</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53723</t>
+          <t>61317</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>52948</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99192</t>
+          <t>114264</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>38045; 65119</t>
+          <t>37656; 64517</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>36614; 66477</t>
+          <t>35889; 64564</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>58153; 92539</t>
+          <t>60191; 90818</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>25716; 79341</t>
+          <t>49728; 76329</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>39104; 67750</t>
+          <t>39546; 67566</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35673; 64531</t>
+          <t>35999; 63763</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>59307; 94508</t>
+          <t>58410; 93299</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>35804; 57083</t>
+          <t>42573; 66031</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>81883; 122654</t>
+          <t>82790; 121128</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>81268; 120829</t>
+          <t>79747; 121622</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>125531; 171242</t>
+          <t>124842; 173155</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>63315; 124474</t>
+          <t>96243; 133124</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>299869</t>
+          <t>328160</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>263819</t>
+          <t>291814</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>563688</t>
+          <t>619974</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>161041; 210802</t>
+          <t>163060; 212361</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>226653; 288927</t>
+          <t>226560; 292023</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>268492; 332542</t>
+          <t>266855; 331080</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>235490; 339621</t>
+          <t>295171; 360639</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>201167; 258756</t>
+          <t>201539; 255318</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>274080; 342156</t>
+          <t>273925; 343177</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>263158; 337702</t>
+          <t>262473; 336372</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>210216; 294073</t>
+          <t>265737; 316192</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>380100; 455760</t>
+          <t>377762; 457589</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>518037; 611320</t>
+          <t>521469; 609828</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>548885; 646291</t>
+          <t>548676; 639499</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>484867; 617312</t>
+          <t>575425; 656432</t>
         </is>
       </c>
     </row>
